--- a/User Manual Source/VECTO Input Parameters.xlsx
+++ b/User Manual Source/VECTO Input Parameters.xlsx
@@ -1,37 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="DieseArbeitsmappe" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krisper\Documents\vecto-sim\User Manual Source\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="45" windowWidth="14025" windowHeight="14430" tabRatio="856"/>
+    <workbookView xWindow="-15" yWindow="45" windowWidth="14025" windowHeight="14430" tabRatio="856" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Changelog" sheetId="24" r:id="rId1"/>
-    <sheet name="VECTO parameters" sheetId="1" r:id="rId2"/>
-    <sheet name="Segment Table" sheetId="4" r:id="rId3"/>
-    <sheet name="ENUM" sheetId="27" r:id="rId4"/>
-    <sheet name="RRC" sheetId="25" r:id="rId5"/>
-    <sheet name="Eng Inertia" sheetId="23" r:id="rId6"/>
-    <sheet name="Gearbox" sheetId="7" r:id="rId7"/>
-    <sheet name="Loading" sheetId="20" r:id="rId8"/>
-    <sheet name="PT1" sheetId="6" r:id="rId9"/>
-    <sheet name="Wheels" sheetId="10" r:id="rId10"/>
-    <sheet name="Aux-ES" sheetId="16" r:id="rId11"/>
-    <sheet name="Aux-Fan" sheetId="13" r:id="rId12"/>
-    <sheet name="Aux-SP" sheetId="14" r:id="rId13"/>
-    <sheet name="Aux-HVAC" sheetId="15" r:id="rId14"/>
-    <sheet name="Aux-PS" sheetId="18" r:id="rId15"/>
-    <sheet name="WHTC-Correction" sheetId="22" r:id="rId16"/>
-    <sheet name="VACC" sheetId="29" r:id="rId17"/>
-    <sheet name="VTCC" sheetId="26" r:id="rId18"/>
-    <sheet name="CdA" sheetId="28" r:id="rId19"/>
+    <sheet name="Structure" sheetId="30" r:id="rId2"/>
+    <sheet name="VECTO parameters" sheetId="1" r:id="rId3"/>
+    <sheet name="Segment Table" sheetId="4" r:id="rId4"/>
+    <sheet name="ENUM" sheetId="27" r:id="rId5"/>
+    <sheet name="RRC" sheetId="25" r:id="rId6"/>
+    <sheet name="Eng Inertia" sheetId="23" r:id="rId7"/>
+    <sheet name="Gearbox" sheetId="7" r:id="rId8"/>
+    <sheet name="Loading" sheetId="20" r:id="rId9"/>
+    <sheet name="PT1" sheetId="6" r:id="rId10"/>
+    <sheet name="Wheels" sheetId="10" r:id="rId11"/>
+    <sheet name="Aux-ES" sheetId="16" r:id="rId12"/>
+    <sheet name="Aux-Fan" sheetId="13" r:id="rId13"/>
+    <sheet name="Aux-SP" sheetId="14" r:id="rId14"/>
+    <sheet name="Aux-HVAC" sheetId="15" r:id="rId15"/>
+    <sheet name="Aux-PS" sheetId="18" r:id="rId16"/>
+    <sheet name="WHTC-Correction" sheetId="22" r:id="rId17"/>
+    <sheet name="VACC" sheetId="29" r:id="rId18"/>
+    <sheet name="VTCC" sheetId="26" r:id="rId19"/>
+    <sheet name="CdA" sheetId="28" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Segment Table'!$D$7:$J$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'VECTO parameters'!$B$3:$O$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Segment Table'!$D$7:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'VECTO parameters'!$B$3:$O$143</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -41,7 +47,7 @@
     <author>Luz Raphael</author>
   </authors>
   <commentList>
-    <comment ref="AA9" authorId="0">
+    <comment ref="AA9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -65,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB9" authorId="0">
+    <comment ref="AB9" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -89,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z10" authorId="0">
+    <comment ref="Z10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -113,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA10" authorId="0">
+    <comment ref="AA10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -137,7 +143,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB10" authorId="0">
+    <comment ref="AB10" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -161,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA11" authorId="0">
+    <comment ref="AA11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -185,7 +191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB11" authorId="0">
+    <comment ref="AB11" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -209,7 +215,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z12" authorId="0">
+    <comment ref="Z12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -233,7 +239,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA12" authorId="0">
+    <comment ref="AA12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -257,7 +263,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC12" authorId="0">
+    <comment ref="AC12" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -281,7 +287,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z13" authorId="0">
+    <comment ref="Z13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -305,7 +311,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA13" authorId="0">
+    <comment ref="AA13" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -329,7 +335,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z17" authorId="0">
+    <comment ref="Z17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -353,7 +359,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA17" authorId="0">
+    <comment ref="AA17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -377,7 +383,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC17" authorId="0">
+    <comment ref="AC17" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -401,7 +407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z18" authorId="0">
+    <comment ref="Z18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -425,7 +431,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA18" authorId="0">
+    <comment ref="AA18" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -459,7 +465,7 @@
     <author>Luz Raphael</author>
   </authors>
   <commentList>
-    <comment ref="I4" authorId="0">
+    <comment ref="I4" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -489,7 +495,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="921">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2902" uniqueCount="971">
   <si>
     <t>Parameter</t>
   </si>
@@ -3450,6 +3456,156 @@
   <si>
     <t>GVW [t]</t>
   </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>MakeModel</t>
+  </si>
+  <si>
+    <t>Type ID</t>
+  </si>
+  <si>
+    <t>Creator</t>
+  </si>
+  <si>
+    <t>VehicleCategory</t>
+  </si>
+  <si>
+    <t>AxleConfiguration</t>
+  </si>
+  <si>
+    <t>CurbWeightChassis</t>
+  </si>
+  <si>
+    <t>CurbWeightBody</t>
+  </si>
+  <si>
+    <t>CurbWeightTrailer</t>
+  </si>
+  <si>
+    <t>Payload</t>
+  </si>
+  <si>
+    <t>GVM</t>
+  </si>
+  <si>
+    <t>CdxA</t>
+  </si>
+  <si>
+    <t>Components</t>
+  </si>
+  <si>
+    <t>Engine</t>
+  </si>
+  <si>
+    <t>Gearbox</t>
+  </si>
+  <si>
+    <t>Fullload</t>
+  </si>
+  <si>
+    <t>LossMaps</t>
+  </si>
+  <si>
+    <t>TorqueConverter</t>
+  </si>
+  <si>
+    <t>ShiftPolygons</t>
+  </si>
+  <si>
+    <t>Retarder</t>
+  </si>
+  <si>
+    <t>AxleGear</t>
+  </si>
+  <si>
+    <t>AxleWheels</t>
+  </si>
+  <si>
+    <t>&lt;Type=Driven&gt;</t>
+  </si>
+  <si>
+    <t>Types:</t>
+  </si>
+  <si>
+    <t>&lt;Type=Twin&gt;</t>
+  </si>
+  <si>
+    <t>VehicleDriven</t>
+  </si>
+  <si>
+    <t>DynamicTireRadius</t>
+  </si>
+  <si>
+    <t>VehicleNonDriven</t>
+  </si>
+  <si>
+    <t>Tyre</t>
+  </si>
+  <si>
+    <t>Trailer</t>
+  </si>
+  <si>
+    <t>Dimension</t>
+  </si>
+  <si>
+    <t>FzIso</t>
+  </si>
+  <si>
+    <t>…</t>
+  </si>
+  <si>
+    <t>Auxiliaries</t>
+  </si>
+  <si>
+    <t>ADAS</t>
+  </si>
+  <si>
+    <t>EngineStartStop</t>
+  </si>
+  <si>
+    <t>Enables=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min delaytime </t>
+  </si>
+  <si>
+    <t>EcoRoll</t>
+  </si>
+  <si>
+    <t>Predictive …</t>
+  </si>
+  <si>
+    <t>Cycles</t>
+  </si>
+  <si>
+    <t>SimulationParameters</t>
+  </si>
+  <si>
+    <t>Overspeed</t>
+  </si>
+  <si>
+    <t>LookAheadCoasting</t>
+  </si>
+  <si>
+    <t>Acc/Dec curves</t>
+  </si>
+  <si>
+    <t>CdCorrectionMode</t>
+  </si>
+  <si>
+    <t>WindSpeed</t>
+  </si>
+  <si>
+    <t>FuelParameters</t>
+  </si>
+  <si>
+    <t>Density</t>
+  </si>
 </sst>
 </file>
 
@@ -3459,7 +3615,7 @@
     <numFmt numFmtId="164" formatCode="000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3739,6 +3895,13 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -5242,7 +5405,7 @@
     <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="472">
+  <cellXfs count="474">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
@@ -6113,12 +6276,82 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="97" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -6131,42 +6364,6 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="76" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -6185,6 +6382,39 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="93" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -6209,30 +6439,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="79" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -6254,15 +6460,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="90" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="91" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6281,40 +6478,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -6409,6 +6574,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -6416,7 +6584,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6450,9 +6618,12 @@
             <c:strRef>
               <c:f>'Eng Inertia'!$D$11:$D$12</c:f>
               <c:strCache>
-                <c:ptCount val="1"/>
+                <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>Inertia including Flywheel and Clutch  [kgm²]</c:v>
+                  <c:v>Inertia including Flywheel and Clutch </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>[kgm²]</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -6554,11 +6725,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="229438592"/>
-        <c:axId val="229440512"/>
+        <c:axId val="304888824"/>
+        <c:axId val="304889216"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="229438592"/>
+        <c:axId val="304888824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="4000"/>
@@ -6582,21 +6753,20 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="#,##0" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="229440512"/>
+        <c:crossAx val="304889216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="2000"/>
         <c:minorUnit val="1000"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="229440512"/>
+        <c:axId val="304889216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="2"/>
@@ -6620,14 +6790,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.00" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="229438592"/>
+        <c:crossAx val="304888824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6647,7 +6816,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -6794,11 +6963,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="231634432"/>
-        <c:axId val="231977344"/>
+        <c:axId val="304890000"/>
+        <c:axId val="304890392"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="231634432"/>
+        <c:axId val="304890000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="7"/>
@@ -6822,20 +6991,19 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="231977344"/>
+        <c:crossAx val="304890392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="1"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="231977344"/>
+        <c:axId val="304890392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -6858,14 +7026,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="231634432"/>
+        <c:crossAx val="304890000"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -6904,7 +7071,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7036,11 +7203,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="103675008"/>
-        <c:axId val="103676928"/>
+        <c:axId val="304891176"/>
+        <c:axId val="304891568"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="103675008"/>
+        <c:axId val="304891176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7062,19 +7229,18 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103676928"/>
+        <c:crossAx val="304891568"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="103676928"/>
+        <c:axId val="304891568"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7097,14 +7263,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103675008"/>
+        <c:crossAx val="304891176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7143,7 +7308,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7312,11 +7477,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="103940864"/>
-        <c:axId val="103942784"/>
+        <c:axId val="304892352"/>
+        <c:axId val="304892744"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="103940864"/>
+        <c:axId val="304892352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7339,19 +7504,18 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103942784"/>
+        <c:crossAx val="304892744"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="103942784"/>
+        <c:axId val="304892744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7374,14 +7538,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103940864"/>
+        <c:crossAx val="304892352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7420,7 +7583,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7558,8 +7721,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="103969536"/>
-        <c:axId val="103971456"/>
+        <c:axId val="307619472"/>
+        <c:axId val="307619864"/>
       </c:scatterChart>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -7675,11 +7838,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="103987840"/>
-        <c:axId val="103985920"/>
+        <c:axId val="307620648"/>
+        <c:axId val="307620256"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="103969536"/>
+        <c:axId val="307619472"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="1"/>
@@ -7703,19 +7866,18 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103971456"/>
+        <c:crossAx val="307619864"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="103971456"/>
+        <c:axId val="307619864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7738,19 +7900,18 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103969536"/>
+        <c:crossAx val="307619472"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="103985920"/>
+        <c:axId val="307620256"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7772,19 +7933,18 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103987840"/>
+        <c:crossAx val="307620648"/>
         <c:crosses val="max"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="103987840"/>
+        <c:axId val="307620648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7794,7 +7954,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="103985920"/>
+        <c:crossAx val="307620256"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -7833,7 +7993,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7961,11 +8121,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="111541248"/>
-        <c:axId val="111588480"/>
+        <c:axId val="307621432"/>
+        <c:axId val="307621824"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="111541248"/>
+        <c:axId val="307621432"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7993,19 +8153,18 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="111588480"/>
+        <c:crossAx val="307621824"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="111588480"/>
+        <c:axId val="307621824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8028,14 +8187,13 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="111541248"/>
+        <c:crossAx val="307621432"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -8323,9 +8481,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8363,9 +8521,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8400,7 +8558,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8435,7 +8593,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8929,6 +9087,156 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr codeName="Tabelle4"/>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.5703125" style="36" customWidth="1"/>
+    <col min="2" max="2" width="7.28515625" style="15" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="15" customWidth="1"/>
+    <col min="4" max="4" width="22" style="15" customWidth="1"/>
+    <col min="5" max="5" width="5.28515625" style="15" customWidth="1"/>
+    <col min="6" max="7" width="22" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:12" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="328" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="3" spans="3:12" s="36" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C3" s="39" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="4" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="D4" s="87" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C5" s="59">
+        <v>400</v>
+      </c>
+      <c r="D5" s="24">
+        <v>0</v>
+      </c>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+    </row>
+    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C6" s="10">
+        <v>800</v>
+      </c>
+      <c r="D6" s="11">
+        <v>0.47</v>
+      </c>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+    </row>
+    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C7" s="10">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="11">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+    </row>
+    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C8" s="10">
+        <v>1200</v>
+      </c>
+      <c r="D8" s="11">
+        <v>0.53</v>
+      </c>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="36"/>
+    </row>
+    <row r="9" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C9" s="10">
+        <v>1400</v>
+      </c>
+      <c r="D9" s="11">
+        <v>0.46</v>
+      </c>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+    </row>
+    <row r="10" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C10" s="10">
+        <v>1500</v>
+      </c>
+      <c r="D10" s="11">
+        <v>0.43</v>
+      </c>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="J10" s="36"/>
+    </row>
+    <row r="11" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C11" s="10">
+        <v>1750</v>
+      </c>
+      <c r="D11" s="11">
+        <v>0.22</v>
+      </c>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="36"/>
+    </row>
+    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C12" s="10">
+        <v>1800</v>
+      </c>
+      <c r="D12" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+    </row>
+    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C13" s="10">
+        <v>2000</v>
+      </c>
+      <c r="D13" s="11">
+        <v>0.11</v>
+      </c>
+      <c r="E13" s="36"/>
+      <c r="F13" s="36"/>
+    </row>
+    <row r="14" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="60">
+        <v>2500</v>
+      </c>
+      <c r="D14" s="61">
+        <v>0.11</v>
+      </c>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle6"/>
   <dimension ref="B1:N44"/>
@@ -10028,7 +10336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:L13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10215,7 +10523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10676,7 +10984,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11225,7 +11533,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:L19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11733,7 +12041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12240,7 +12548,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:N8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12429,7 +12737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12532,7 +12840,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12703,7 +13011,312 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:I63"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="11.42578125" style="36"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="36" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="36" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="36" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="36" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="36" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="36" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C8" s="36" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="36" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="36" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="472" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C12" s="472" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="472" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="36" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="36" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C16" s="36" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D17" s="36" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="18" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D18" s="36" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="19" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E19" s="36" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="20" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E20" s="36" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="21" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E21" s="36" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="22" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E22" s="36" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="23" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D23" s="36" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="24" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D24" s="36" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="25" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D25" s="36" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="26" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E26" s="36" t="s">
+        <v>944</v>
+      </c>
+      <c r="H26" s="36" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="27" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E27" s="36" t="s">
+        <v>946</v>
+      </c>
+      <c r="I27" s="36" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="28" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E28" s="473" t="s">
+        <v>948</v>
+      </c>
+      <c r="I28" s="36" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="29" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="E29" s="36" t="s">
+        <v>950</v>
+      </c>
+      <c r="I29" s="36" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="30" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F30" s="36" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="31" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F31" s="36" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="32" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="F32" s="36" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F33" s="36" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F34" s="36" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F35" s="36" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F36" s="36" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F37" s="36" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="F38" s="36" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D39" s="36" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C44" s="36" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D45" s="36" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E46" s="36" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="47" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="472" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="48" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="D48" s="36" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D49" s="36" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="472" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="472" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C54" s="472" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C55" s="472" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C56" s="472" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C57" s="472" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C58" s="472" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C59" s="472" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C60" s="472" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D61" s="36" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D62" s="36" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D63" s="36" t="s">
+        <v>548</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:E25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12917,7 +13530,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle1"/>
   <dimension ref="B1:O151"/>
@@ -12943,21 +13556,21 @@
   <sheetData>
     <row r="1" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:15" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="407" t="s">
+      <c r="B2" s="431" t="s">
         <v>280</v>
       </c>
-      <c r="C2" s="408"/>
-      <c r="D2" s="408"/>
-      <c r="E2" s="408"/>
-      <c r="F2" s="408"/>
-      <c r="G2" s="409"/>
-      <c r="H2" s="407" t="s">
+      <c r="C2" s="432"/>
+      <c r="D2" s="432"/>
+      <c r="E2" s="432"/>
+      <c r="F2" s="432"/>
+      <c r="G2" s="433"/>
+      <c r="H2" s="431" t="s">
         <v>279</v>
       </c>
-      <c r="I2" s="408"/>
-      <c r="J2" s="408"/>
-      <c r="K2" s="408"/>
-      <c r="L2" s="409"/>
+      <c r="I2" s="432"/>
+      <c r="J2" s="432"/>
+      <c r="K2" s="432"/>
+      <c r="L2" s="433"/>
       <c r="M2" s="331" t="s">
         <v>654</v>
       </c>
@@ -13169,7 +13782,7 @@
       <c r="C8" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="406" t="s">
+      <c r="D8" s="430" t="s">
         <v>507</v>
       </c>
       <c r="E8" s="25" t="s">
@@ -13207,7 +13820,7 @@
       <c r="C9" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D9" s="406"/>
+      <c r="D9" s="430"/>
       <c r="E9" s="25" t="s">
         <v>241</v>
       </c>
@@ -13245,7 +13858,7 @@
       <c r="C10" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="406"/>
+      <c r="D10" s="430"/>
       <c r="E10" s="25" t="s">
         <v>419</v>
       </c>
@@ -13283,7 +13896,7 @@
       <c r="C11" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="406"/>
+      <c r="D11" s="430"/>
       <c r="E11" s="25" t="s">
         <v>418</v>
       </c>
@@ -13321,7 +13934,7 @@
       <c r="C12" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="406"/>
+      <c r="D12" s="430"/>
       <c r="E12" s="25" t="s">
         <v>801</v>
       </c>
@@ -13891,7 +14504,7 @@
       <c r="C26" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D26" s="414" t="s">
+      <c r="D26" s="420" t="s">
         <v>494</v>
       </c>
       <c r="E26" s="25" t="s">
@@ -13931,7 +14544,7 @@
       <c r="C27" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="415"/>
+      <c r="D27" s="421"/>
       <c r="E27" s="25" t="s">
         <v>65</v>
       </c>
@@ -13969,7 +14582,7 @@
       <c r="C28" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="415"/>
+      <c r="D28" s="421"/>
       <c r="E28" s="25" t="s">
         <v>66</v>
       </c>
@@ -14007,7 +14620,7 @@
       <c r="C29" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D29" s="415"/>
+      <c r="D29" s="421"/>
       <c r="E29" s="25" t="s">
         <v>242</v>
       </c>
@@ -14045,7 +14658,7 @@
       <c r="C30" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="415"/>
+      <c r="D30" s="421"/>
       <c r="E30" s="25" t="s">
         <v>243</v>
       </c>
@@ -14083,7 +14696,7 @@
       <c r="C31" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="416"/>
+      <c r="D31" s="422"/>
       <c r="E31" s="26" t="s">
         <v>244</v>
       </c>
@@ -14121,7 +14734,7 @@
       <c r="C32" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="417" t="s">
+      <c r="D32" s="423" t="s">
         <v>494</v>
       </c>
       <c r="E32" s="2" t="s">
@@ -14159,7 +14772,7 @@
       <c r="C33" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D33" s="418"/>
+      <c r="D33" s="424"/>
       <c r="E33" s="2" t="s">
         <v>246</v>
       </c>
@@ -14195,7 +14808,7 @@
       <c r="C34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D34" s="418"/>
+      <c r="D34" s="424"/>
       <c r="E34" s="2" t="s">
         <v>247</v>
       </c>
@@ -14231,7 +14844,7 @@
       <c r="C35" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="418"/>
+      <c r="D35" s="424"/>
       <c r="E35" s="2" t="s">
         <v>248</v>
       </c>
@@ -14267,7 +14880,7 @@
       <c r="C36" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D36" s="418"/>
+      <c r="D36" s="424"/>
       <c r="E36" s="25" t="s">
         <v>249</v>
       </c>
@@ -14305,7 +14918,7 @@
       <c r="C37" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="418"/>
+      <c r="D37" s="424"/>
       <c r="E37" s="25" t="s">
         <v>425</v>
       </c>
@@ -14343,7 +14956,7 @@
       <c r="C38" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="418"/>
+      <c r="D38" s="424"/>
       <c r="E38" s="25" t="s">
         <v>262</v>
       </c>
@@ -14381,7 +14994,7 @@
       <c r="C39" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="418"/>
+      <c r="D39" s="424"/>
       <c r="E39" s="25" t="s">
         <v>426</v>
       </c>
@@ -14419,7 +15032,7 @@
       <c r="C40" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D40" s="418"/>
+      <c r="D40" s="424"/>
       <c r="E40" s="25" t="s">
         <v>427</v>
       </c>
@@ -14457,7 +15070,7 @@
       <c r="C41" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D41" s="418"/>
+      <c r="D41" s="424"/>
       <c r="E41" s="25" t="s">
         <v>428</v>
       </c>
@@ -14495,7 +15108,7 @@
       <c r="C42" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D42" s="418"/>
+      <c r="D42" s="424"/>
       <c r="E42" s="25" t="s">
         <v>429</v>
       </c>
@@ -14533,7 +15146,7 @@
       <c r="C43" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="D43" s="418"/>
+      <c r="D43" s="424"/>
       <c r="E43" s="25" t="s">
         <v>430</v>
       </c>
@@ -14571,7 +15184,7 @@
       <c r="C44" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="D44" s="419"/>
+      <c r="D44" s="425"/>
       <c r="E44" s="26" t="s">
         <v>431</v>
       </c>
@@ -14609,7 +15222,7 @@
       <c r="C45" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D45" s="414" t="s">
+      <c r="D45" s="420" t="s">
         <v>494</v>
       </c>
       <c r="E45" s="25" t="s">
@@ -14647,7 +15260,7 @@
       <c r="C46" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="D46" s="415"/>
+      <c r="D46" s="421"/>
       <c r="E46" s="25" t="s">
         <v>251</v>
       </c>
@@ -14683,7 +15296,7 @@
       <c r="C47" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="D47" s="416"/>
+      <c r="D47" s="422"/>
       <c r="E47" s="26" t="s">
         <v>252</v>
       </c>
@@ -14828,7 +15441,7 @@
       <c r="N50" s="74">
         <v>40000</v>
       </c>
-      <c r="O50" s="410" t="s">
+      <c r="O50" s="416" t="s">
         <v>453</v>
       </c>
     </row>
@@ -14870,7 +15483,7 @@
       <c r="N51" s="74">
         <v>40000</v>
       </c>
-      <c r="O51" s="410"/>
+      <c r="O51" s="416"/>
     </row>
     <row r="52" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B52" s="249" t="s">
@@ -14910,7 +15523,7 @@
       <c r="N52" s="74">
         <v>40000</v>
       </c>
-      <c r="O52" s="410"/>
+      <c r="O52" s="416"/>
     </row>
     <row r="53" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B53" s="249" t="s">
@@ -14948,7 +15561,7 @@
       <c r="N53" s="74">
         <v>40000</v>
       </c>
-      <c r="O53" s="410"/>
+      <c r="O53" s="416"/>
     </row>
     <row r="54" spans="2:15" ht="30" x14ac:dyDescent="0.25">
       <c r="B54" s="249" t="s">
@@ -15037,7 +15650,7 @@
       <c r="C56" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D56" s="405" t="s">
+      <c r="D56" s="426" t="s">
         <v>508</v>
       </c>
       <c r="E56" s="2" t="s">
@@ -15079,7 +15692,7 @@
       <c r="C57" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="405"/>
+      <c r="D57" s="426"/>
       <c r="E57" s="25" t="s">
         <v>254</v>
       </c>
@@ -15115,7 +15728,7 @@
       <c r="C58" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D58" s="405"/>
+      <c r="D58" s="426"/>
       <c r="E58" s="2" t="s">
         <v>255</v>
       </c>
@@ -15151,7 +15764,7 @@
       <c r="C59" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D59" s="405"/>
+      <c r="D59" s="426"/>
       <c r="E59" s="2" t="s">
         <v>256</v>
       </c>
@@ -15187,7 +15800,7 @@
       <c r="C60" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D60" s="405"/>
+      <c r="D60" s="426"/>
       <c r="E60" s="25" t="s">
         <v>445</v>
       </c>
@@ -15225,7 +15838,7 @@
       <c r="C61" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D61" s="405"/>
+      <c r="D61" s="426"/>
       <c r="E61" s="25" t="s">
         <v>444</v>
       </c>
@@ -15539,7 +16152,7 @@
       <c r="C69" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D69" s="417" t="s">
+      <c r="D69" s="423" t="s">
         <v>494</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -15577,7 +16190,7 @@
       <c r="C70" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D70" s="419"/>
+      <c r="D70" s="425"/>
       <c r="E70" s="4" t="s">
         <v>257</v>
       </c>
@@ -15613,7 +16226,7 @@
       <c r="C71" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="D71" s="417" t="s">
+      <c r="D71" s="423" t="s">
         <v>494</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -15651,7 +16264,7 @@
       <c r="C72" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="D72" s="419"/>
+      <c r="D72" s="425"/>
       <c r="E72" s="4" t="s">
         <v>259</v>
       </c>
@@ -15946,7 +16559,7 @@
       <c r="N79" s="74" t="s">
         <v>458</v>
       </c>
-      <c r="O79" s="420" t="s">
+      <c r="O79" s="427" t="s">
         <v>457</v>
       </c>
     </row>
@@ -15986,7 +16599,7 @@
       <c r="N80" s="74" t="s">
         <v>458</v>
       </c>
-      <c r="O80" s="420"/>
+      <c r="O80" s="427"/>
     </row>
     <row r="81" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="252" t="s">
@@ -16024,7 +16637,7 @@
       <c r="N81" s="78" t="s">
         <v>458</v>
       </c>
-      <c r="O81" s="421"/>
+      <c r="O81" s="428"/>
     </row>
     <row r="82" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B82" s="249" t="s">
@@ -16033,7 +16646,7 @@
       <c r="C82" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D82" s="417" t="s">
+      <c r="D82" s="423" t="s">
         <v>494</v>
       </c>
       <c r="E82" s="2" t="s">
@@ -16071,7 +16684,7 @@
       <c r="C83" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D83" s="418"/>
+      <c r="D83" s="424"/>
       <c r="E83" s="6" t="s">
         <v>263</v>
       </c>
@@ -16107,7 +16720,7 @@
       <c r="C84" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D84" s="418"/>
+      <c r="D84" s="424"/>
       <c r="E84" s="2" t="s">
         <v>264</v>
       </c>
@@ -16143,7 +16756,7 @@
       <c r="C85" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="D85" s="419"/>
+      <c r="D85" s="425"/>
       <c r="E85" s="26" t="s">
         <v>265</v>
       </c>
@@ -16181,7 +16794,7 @@
       <c r="C86" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D86" s="417" t="s">
+      <c r="D86" s="423" t="s">
         <v>494</v>
       </c>
       <c r="E86" s="2" t="s">
@@ -16219,7 +16832,7 @@
       <c r="C87" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D87" s="418"/>
+      <c r="D87" s="424"/>
       <c r="E87" s="6" t="s">
         <v>266</v>
       </c>
@@ -16255,7 +16868,7 @@
       <c r="C88" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D88" s="419"/>
+      <c r="D88" s="425"/>
       <c r="E88" s="4" t="s">
         <v>267</v>
       </c>
@@ -16369,7 +16982,7 @@
       <c r="C91" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D91" s="406" t="s">
+      <c r="D91" s="430" t="s">
         <v>832</v>
       </c>
       <c r="E91" s="25" t="s">
@@ -16409,7 +17022,7 @@
       <c r="C92" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D92" s="406"/>
+      <c r="D92" s="430"/>
       <c r="E92" s="25" t="s">
         <v>396</v>
       </c>
@@ -16449,7 +17062,7 @@
       <c r="C93" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D93" s="406"/>
+      <c r="D93" s="430"/>
       <c r="E93" s="25" t="s">
         <v>268</v>
       </c>
@@ -16487,7 +17100,7 @@
       <c r="C94" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="D94" s="406"/>
+      <c r="D94" s="430"/>
       <c r="E94" s="25" t="s">
         <v>525</v>
       </c>
@@ -16525,7 +17138,7 @@
       <c r="C95" s="349" t="s">
         <v>53</v>
       </c>
-      <c r="D95" s="406"/>
+      <c r="D95" s="430"/>
       <c r="E95" s="349" t="s">
         <v>831</v>
       </c>
@@ -17040,7 +17653,7 @@
       <c r="N107" s="74" t="s">
         <v>12</v>
       </c>
-      <c r="O107" s="412" t="s">
+      <c r="O107" s="418" t="s">
         <v>469</v>
       </c>
     </row>
@@ -17080,7 +17693,7 @@
       <c r="N108" s="78">
         <v>10</v>
       </c>
-      <c r="O108" s="413"/>
+      <c r="O108" s="419"/>
     </row>
     <row r="109" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B109" s="249" t="s">
@@ -17089,7 +17702,7 @@
       <c r="C109" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D109" s="417" t="s">
+      <c r="D109" s="423" t="s">
         <v>494</v>
       </c>
       <c r="E109" s="2" t="s">
@@ -17129,7 +17742,7 @@
       <c r="C110" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D110" s="418"/>
+      <c r="D110" s="424"/>
       <c r="E110" s="2" t="s">
         <v>270</v>
       </c>
@@ -17167,7 +17780,7 @@
       <c r="C111" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D111" s="419"/>
+      <c r="D111" s="425"/>
       <c r="E111" s="4" t="s">
         <v>271</v>
       </c>
@@ -17205,7 +17818,7 @@
       <c r="C112" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="D112" s="417" t="s">
+      <c r="D112" s="423" t="s">
         <v>494</v>
       </c>
       <c r="E112" s="2" t="s">
@@ -17243,7 +17856,7 @@
       <c r="C113" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="D113" s="418"/>
+      <c r="D113" s="424"/>
       <c r="E113" s="2" t="s">
         <v>273</v>
       </c>
@@ -17279,7 +17892,7 @@
       <c r="C114" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="D114" s="419"/>
+      <c r="D114" s="425"/>
       <c r="E114" s="4" t="s">
         <v>274</v>
       </c>
@@ -17315,7 +17928,7 @@
       <c r="C115" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D115" s="417" t="s">
+      <c r="D115" s="423" t="s">
         <v>494</v>
       </c>
       <c r="E115" s="2" t="s">
@@ -17346,7 +17959,7 @@
       <c r="N115" s="74">
         <v>1</v>
       </c>
-      <c r="O115" s="411" t="s">
+      <c r="O115" s="417" t="s">
         <v>471</v>
       </c>
     </row>
@@ -17357,7 +17970,7 @@
       <c r="C116" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D116" s="418"/>
+      <c r="D116" s="424"/>
       <c r="E116" s="2" t="s">
         <v>713</v>
       </c>
@@ -17386,7 +17999,7 @@
       <c r="N116" s="74" t="s">
         <v>466</v>
       </c>
-      <c r="O116" s="412"/>
+      <c r="O116" s="418"/>
     </row>
     <row r="117" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B117" s="251" t="s">
@@ -17395,7 +18008,7 @@
       <c r="C117" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="D117" s="419"/>
+      <c r="D117" s="425"/>
       <c r="E117" s="4" t="s">
         <v>275</v>
       </c>
@@ -17424,7 +18037,7 @@
       <c r="N117" s="78" t="s">
         <v>451</v>
       </c>
-      <c r="O117" s="413"/>
+      <c r="O117" s="419"/>
     </row>
     <row r="118" spans="2:15" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B118" s="250" t="s">
@@ -18434,7 +19047,7 @@
       <c r="C146" s="336" t="s">
         <v>52</v>
       </c>
-      <c r="D146" s="404" t="s">
+      <c r="D146" s="429" t="s">
         <v>519</v>
       </c>
       <c r="E146" s="336" t="s">
@@ -18472,7 +19085,7 @@
       <c r="C147" s="342" t="s">
         <v>52</v>
       </c>
-      <c r="D147" s="405"/>
+      <c r="D147" s="426"/>
       <c r="E147" s="342" t="s">
         <v>261</v>
       </c>
@@ -18665,6 +19278,11 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="D146:D147"/>
+    <mergeCell ref="D91:D95"/>
+    <mergeCell ref="D8:D12"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="H2:L2"/>
     <mergeCell ref="O50:O53"/>
     <mergeCell ref="O115:O117"/>
     <mergeCell ref="D26:D31"/>
@@ -18680,11 +19298,6 @@
     <mergeCell ref="D56:D61"/>
     <mergeCell ref="O79:O81"/>
     <mergeCell ref="O107:O108"/>
-    <mergeCell ref="D146:D147"/>
-    <mergeCell ref="D91:D95"/>
-    <mergeCell ref="D8:D12"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="H2:L2"/>
   </mergeCells>
   <conditionalFormatting sqref="H94 H96:H139 H4:H90 H145:H1022">
     <cfRule type="expression" dxfId="5" priority="9">
@@ -18721,7 +19334,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle3"/>
   <dimension ref="B1:AU32"/>
@@ -18756,62 +19369,62 @@
       <c r="E2" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="F2" s="422" t="s">
+      <c r="F2" s="434" t="s">
         <v>336</v>
       </c>
-      <c r="G2" s="423"/>
+      <c r="G2" s="435"/>
       <c r="H2" s="278" t="s">
         <v>154</v>
       </c>
       <c r="I2" s="278" t="s">
         <v>102</v>
       </c>
-      <c r="J2" s="422" t="s">
+      <c r="J2" s="434" t="s">
         <v>113</v>
       </c>
-      <c r="K2" s="423"/>
-      <c r="L2" s="422" t="s">
+      <c r="K2" s="435"/>
+      <c r="L2" s="434" t="s">
         <v>110</v>
       </c>
-      <c r="M2" s="424"/>
-      <c r="N2" s="424"/>
-      <c r="O2" s="423"/>
-      <c r="P2" s="422" t="s">
+      <c r="M2" s="436"/>
+      <c r="N2" s="436"/>
+      <c r="O2" s="435"/>
+      <c r="P2" s="434" t="s">
         <v>101</v>
       </c>
-      <c r="Q2" s="424"/>
-      <c r="R2" s="424"/>
-      <c r="S2" s="424"/>
-      <c r="T2" s="424"/>
-      <c r="U2" s="424"/>
-      <c r="V2" s="424"/>
-      <c r="W2" s="424"/>
-      <c r="X2" s="424"/>
-      <c r="Y2" s="423"/>
-      <c r="Z2" s="425" t="s">
+      <c r="Q2" s="436"/>
+      <c r="R2" s="436"/>
+      <c r="S2" s="436"/>
+      <c r="T2" s="436"/>
+      <c r="U2" s="436"/>
+      <c r="V2" s="436"/>
+      <c r="W2" s="436"/>
+      <c r="X2" s="436"/>
+      <c r="Y2" s="435"/>
+      <c r="Z2" s="437" t="s">
         <v>108</v>
       </c>
-      <c r="AA2" s="426"/>
-      <c r="AB2" s="426"/>
-      <c r="AC2" s="426"/>
-      <c r="AD2" s="426"/>
-      <c r="AE2" s="426"/>
-      <c r="AF2" s="426"/>
-      <c r="AG2" s="426"/>
-      <c r="AH2" s="426"/>
-      <c r="AI2" s="427"/>
-      <c r="AJ2" s="422" t="s">
+      <c r="AA2" s="438"/>
+      <c r="AB2" s="438"/>
+      <c r="AC2" s="438"/>
+      <c r="AD2" s="438"/>
+      <c r="AE2" s="438"/>
+      <c r="AF2" s="438"/>
+      <c r="AG2" s="438"/>
+      <c r="AH2" s="438"/>
+      <c r="AI2" s="439"/>
+      <c r="AJ2" s="434" t="s">
         <v>109</v>
       </c>
-      <c r="AK2" s="424"/>
-      <c r="AL2" s="424"/>
-      <c r="AM2" s="424"/>
-      <c r="AN2" s="424"/>
-      <c r="AO2" s="424"/>
-      <c r="AP2" s="424"/>
-      <c r="AQ2" s="424"/>
-      <c r="AR2" s="424"/>
-      <c r="AS2" s="423"/>
+      <c r="AK2" s="436"/>
+      <c r="AL2" s="436"/>
+      <c r="AM2" s="436"/>
+      <c r="AN2" s="436"/>
+      <c r="AO2" s="436"/>
+      <c r="AP2" s="436"/>
+      <c r="AQ2" s="436"/>
+      <c r="AR2" s="436"/>
+      <c r="AS2" s="435"/>
       <c r="AT2" s="279"/>
       <c r="AU2" s="279"/>
     </row>
@@ -18951,135 +19564,135 @@
       <c r="AT3"/>
       <c r="AU3"/>
     </row>
-    <row r="4" spans="2:47" s="471" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="460"/>
-      <c r="C4" s="461" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="461" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="461" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="462" t="s">
+    <row r="4" spans="2:47" s="415" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="404"/>
+      <c r="C4" s="405" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="405" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="405" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="406" t="s">
         <v>286</v>
       </c>
-      <c r="G4" s="463" t="s">
+      <c r="G4" s="407" t="s">
         <v>286</v>
       </c>
-      <c r="H4" s="464" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="464" t="s">
-        <v>12</v>
-      </c>
-      <c r="J4" s="462" t="s">
-        <v>12</v>
-      </c>
-      <c r="K4" s="463" t="s">
-        <v>12</v>
-      </c>
-      <c r="L4" s="462" t="s">
-        <v>12</v>
-      </c>
-      <c r="M4" s="465" t="s">
-        <v>12</v>
-      </c>
-      <c r="N4" s="466" t="s">
-        <v>12</v>
-      </c>
-      <c r="O4" s="463" t="s">
-        <v>12</v>
-      </c>
-      <c r="P4" s="462" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="R4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="S4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="T4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="U4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="V4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="W4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="X4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y4" s="467" t="s">
-        <v>12</v>
-      </c>
-      <c r="Z4" s="468" t="s">
+      <c r="H4" s="408" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="408" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" s="406" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="407" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="406" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="409" t="s">
+        <v>12</v>
+      </c>
+      <c r="N4" s="410" t="s">
+        <v>12</v>
+      </c>
+      <c r="O4" s="407" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="406" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="R4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="S4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="T4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="U4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="V4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="W4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="X4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y4" s="411" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z4" s="412" t="s">
         <v>27</v>
       </c>
-      <c r="AA4" s="469" t="s">
+      <c r="AA4" s="413" t="s">
         <v>27</v>
       </c>
-      <c r="AB4" s="469" t="s">
+      <c r="AB4" s="413" t="s">
         <v>27</v>
       </c>
-      <c r="AC4" s="469" t="s">
+      <c r="AC4" s="413" t="s">
         <v>27</v>
       </c>
-      <c r="AD4" s="469" t="s">
+      <c r="AD4" s="413" t="s">
         <v>27</v>
       </c>
-      <c r="AE4" s="469" t="s">
+      <c r="AE4" s="413" t="s">
         <v>27</v>
       </c>
-      <c r="AF4" s="469" t="s">
+      <c r="AF4" s="413" t="s">
         <v>27</v>
       </c>
-      <c r="AG4" s="469" t="s">
+      <c r="AG4" s="413" t="s">
         <v>27</v>
       </c>
-      <c r="AH4" s="469" t="s">
+      <c r="AH4" s="413" t="s">
         <v>27</v>
       </c>
-      <c r="AI4" s="470" t="s">
+      <c r="AI4" s="414" t="s">
         <v>27</v>
       </c>
-      <c r="AJ4" s="462" t="s">
+      <c r="AJ4" s="406" t="s">
         <v>27</v>
       </c>
-      <c r="AK4" s="467" t="s">
+      <c r="AK4" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="AL4" s="467" t="s">
+      <c r="AL4" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="AM4" s="467" t="s">
+      <c r="AM4" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="AN4" s="467" t="s">
+      <c r="AN4" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="AO4" s="467" t="s">
+      <c r="AO4" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="AP4" s="467" t="s">
+      <c r="AP4" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="AQ4" s="467" t="s">
+      <c r="AQ4" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="AR4" s="467" t="s">
+      <c r="AR4" s="411" t="s">
         <v>27</v>
       </c>
-      <c r="AS4" s="463" t="s">
+      <c r="AS4" s="407" t="s">
         <v>27</v>
       </c>
     </row>
@@ -22536,7 +23149,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:G127"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -22568,10 +23181,10 @@
       <c r="B5" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C5" s="436" t="s">
+      <c r="C5" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D5" s="437"/>
+      <c r="D5" s="444"/>
       <c r="G5" s="36"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
@@ -22581,7 +23194,7 @@
       <c r="C6" s="303" t="s">
         <v>684</v>
       </c>
-      <c r="D6" s="451" t="s">
+      <c r="D6" s="440" t="s">
         <v>760</v>
       </c>
       <c r="G6" s="36"/>
@@ -22593,7 +23206,7 @@
       <c r="C7" s="80" t="s">
         <v>685</v>
       </c>
-      <c r="D7" s="452"/>
+      <c r="D7" s="441"/>
       <c r="G7" s="36"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
@@ -22603,7 +23216,7 @@
       <c r="C8" s="80" t="s">
         <v>686</v>
       </c>
-      <c r="D8" s="452"/>
+      <c r="D8" s="441"/>
       <c r="G8" s="36"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -22613,7 +23226,7 @@
       <c r="C9" s="80" t="s">
         <v>683</v>
       </c>
-      <c r="D9" s="452"/>
+      <c r="D9" s="441"/>
       <c r="G9" s="36"/>
     </row>
     <row r="10" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -22623,7 +23236,7 @@
       <c r="C10" s="227" t="s">
         <v>687</v>
       </c>
-      <c r="D10" s="453"/>
+      <c r="D10" s="442"/>
     </row>
     <row r="11" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="12" spans="2:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22641,33 +23254,33 @@
       <c r="B13" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C13" s="436" t="s">
+      <c r="C13" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D13" s="437"/>
+      <c r="D13" s="444"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="304" t="s">
         <v>757</v>
       </c>
-      <c r="C14" s="438" t="s">
+      <c r="C14" s="445" t="s">
         <v>761</v>
       </c>
-      <c r="D14" s="439"/>
+      <c r="D14" s="446"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="223" t="s">
         <v>758</v>
       </c>
-      <c r="C15" s="440"/>
-      <c r="D15" s="441"/>
+      <c r="C15" s="447"/>
+      <c r="D15" s="448"/>
     </row>
     <row r="16" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="225" t="s">
         <v>759</v>
       </c>
-      <c r="C16" s="442"/>
-      <c r="D16" s="443"/>
+      <c r="C16" s="449"/>
+      <c r="D16" s="450"/>
     </row>
     <row r="17" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22685,47 +23298,47 @@
       <c r="B19" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C19" s="436" t="s">
+      <c r="C19" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D19" s="437"/>
+      <c r="D19" s="444"/>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="304" t="s">
         <v>762</v>
       </c>
-      <c r="C20" s="438" t="s">
+      <c r="C20" s="445" t="s">
         <v>798</v>
       </c>
-      <c r="D20" s="439"/>
+      <c r="D20" s="446"/>
     </row>
     <row r="21" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="223" t="s">
         <v>763</v>
       </c>
-      <c r="C21" s="440"/>
-      <c r="D21" s="441"/>
+      <c r="C21" s="447"/>
+      <c r="D21" s="448"/>
     </row>
     <row r="22" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="223" t="s">
         <v>764</v>
       </c>
-      <c r="C22" s="440"/>
-      <c r="D22" s="441"/>
+      <c r="C22" s="447"/>
+      <c r="D22" s="448"/>
     </row>
     <row r="23" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="223" t="s">
         <v>765</v>
       </c>
-      <c r="C23" s="440"/>
-      <c r="D23" s="441"/>
+      <c r="C23" s="447"/>
+      <c r="D23" s="448"/>
     </row>
     <row r="24" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="225" t="s">
         <v>766</v>
       </c>
-      <c r="C24" s="442"/>
-      <c r="D24" s="443"/>
+      <c r="C24" s="449"/>
+      <c r="D24" s="450"/>
     </row>
     <row r="25" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22743,75 +23356,75 @@
       <c r="B27" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C27" s="436" t="s">
+      <c r="C27" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D27" s="437"/>
+      <c r="D27" s="444"/>
     </row>
     <row r="28" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B28" s="304" t="s">
         <v>767</v>
       </c>
-      <c r="C28" s="438" t="s">
+      <c r="C28" s="445" t="s">
         <v>799</v>
       </c>
-      <c r="D28" s="439"/>
+      <c r="D28" s="446"/>
     </row>
     <row r="29" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B29" s="223" t="s">
         <v>768</v>
       </c>
-      <c r="C29" s="440"/>
-      <c r="D29" s="441"/>
+      <c r="C29" s="447"/>
+      <c r="D29" s="448"/>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B30" s="223" t="s">
         <v>769</v>
       </c>
-      <c r="C30" s="440"/>
-      <c r="D30" s="441"/>
+      <c r="C30" s="447"/>
+      <c r="D30" s="448"/>
     </row>
     <row r="31" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B31" s="223" t="s">
         <v>770</v>
       </c>
-      <c r="C31" s="440"/>
-      <c r="D31" s="441"/>
+      <c r="C31" s="447"/>
+      <c r="D31" s="448"/>
     </row>
     <row r="32" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B32" s="223" t="s">
         <v>771</v>
       </c>
-      <c r="C32" s="440"/>
-      <c r="D32" s="441"/>
+      <c r="C32" s="447"/>
+      <c r="D32" s="448"/>
     </row>
     <row r="33" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="223" t="s">
         <v>772</v>
       </c>
-      <c r="C33" s="440"/>
-      <c r="D33" s="441"/>
+      <c r="C33" s="447"/>
+      <c r="D33" s="448"/>
     </row>
     <row r="34" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="223" t="s">
         <v>773</v>
       </c>
-      <c r="C34" s="440"/>
-      <c r="D34" s="441"/>
+      <c r="C34" s="447"/>
+      <c r="D34" s="448"/>
     </row>
     <row r="35" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="223" t="s">
         <v>774</v>
       </c>
-      <c r="C35" s="440"/>
-      <c r="D35" s="441"/>
+      <c r="C35" s="447"/>
+      <c r="D35" s="448"/>
     </row>
     <row r="36" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="225" t="s">
         <v>775</v>
       </c>
-      <c r="C36" s="442"/>
-      <c r="D36" s="443"/>
+      <c r="C36" s="449"/>
+      <c r="D36" s="450"/>
     </row>
     <row r="37" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22829,10 +23442,10 @@
       <c r="B39" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C39" s="436" t="s">
+      <c r="C39" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D39" s="437"/>
+      <c r="D39" s="444"/>
     </row>
     <row r="40" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B40" s="304" t="s">
@@ -22841,7 +23454,7 @@
       <c r="C40" s="303" t="s">
         <v>781</v>
       </c>
-      <c r="D40" s="451" t="s">
+      <c r="D40" s="440" t="s">
         <v>782</v>
       </c>
     </row>
@@ -22852,7 +23465,7 @@
       <c r="C41" s="80" t="s">
         <v>783</v>
       </c>
-      <c r="D41" s="452"/>
+      <c r="D41" s="441"/>
     </row>
     <row r="42" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B42" s="223" t="s">
@@ -22861,7 +23474,7 @@
       <c r="C42" s="80" t="s">
         <v>784</v>
       </c>
-      <c r="D42" s="452"/>
+      <c r="D42" s="441"/>
     </row>
     <row r="43" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="225" t="s">
@@ -22870,7 +23483,7 @@
       <c r="C43" s="227" t="s">
         <v>780</v>
       </c>
-      <c r="D43" s="453"/>
+      <c r="D43" s="442"/>
     </row>
     <row r="44" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="45" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22888,17 +23501,17 @@
       <c r="B46" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C46" s="436" t="s">
+      <c r="C46" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D46" s="437"/>
+      <c r="D46" s="444"/>
     </row>
     <row r="47" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B47" s="304" t="s">
         <v>785</v>
       </c>
       <c r="C47" s="303"/>
-      <c r="D47" s="451"/>
+      <c r="D47" s="440"/>
     </row>
     <row r="48" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B48" s="223" t="s">
@@ -22907,7 +23520,7 @@
       <c r="C48" s="80" t="s">
         <v>789</v>
       </c>
-      <c r="D48" s="452"/>
+      <c r="D48" s="441"/>
     </row>
     <row r="49" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="225" t="s">
@@ -22916,7 +23529,7 @@
       <c r="C49" s="227" t="s">
         <v>788</v>
       </c>
-      <c r="D49" s="453"/>
+      <c r="D49" s="442"/>
     </row>
     <row r="50" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="51" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22934,10 +23547,10 @@
       <c r="B52" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C52" s="436" t="s">
+      <c r="C52" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D52" s="437"/>
+      <c r="D52" s="444"/>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="304" t="s">
@@ -22946,7 +23559,7 @@
       <c r="C53" s="303" t="s">
         <v>795</v>
       </c>
-      <c r="D53" s="451" t="s">
+      <c r="D53" s="440" t="s">
         <v>797</v>
       </c>
     </row>
@@ -22957,7 +23570,7 @@
       <c r="C54" s="80" t="s">
         <v>794</v>
       </c>
-      <c r="D54" s="452"/>
+      <c r="D54" s="441"/>
     </row>
     <row r="55" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B55" s="223" t="s">
@@ -22966,14 +23579,14 @@
       <c r="C55" s="80" t="s">
         <v>796</v>
       </c>
-      <c r="D55" s="452"/>
+      <c r="D55" s="441"/>
     </row>
     <row r="56" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B56" s="225" t="s">
         <v>793</v>
       </c>
       <c r="C56" s="227"/>
-      <c r="D56" s="453"/>
+      <c r="D56" s="442"/>
     </row>
     <row r="57" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -22991,290 +23604,290 @@
       <c r="B59" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C59" s="436" t="s">
+      <c r="C59" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D59" s="437"/>
+      <c r="D59" s="444"/>
     </row>
     <row r="60" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B60" s="304" t="s">
         <v>843</v>
       </c>
-      <c r="C60" s="430"/>
-      <c r="D60" s="431"/>
+      <c r="C60" s="453"/>
+      <c r="D60" s="454"/>
     </row>
     <row r="61" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B61" s="223" t="s">
         <v>844</v>
       </c>
-      <c r="C61" s="432"/>
-      <c r="D61" s="433"/>
+      <c r="C61" s="455"/>
+      <c r="D61" s="456"/>
     </row>
     <row r="62" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B62" s="223" t="s">
         <v>845</v>
       </c>
-      <c r="C62" s="432"/>
-      <c r="D62" s="433"/>
+      <c r="C62" s="455"/>
+      <c r="D62" s="456"/>
     </row>
     <row r="63" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B63" s="223" t="s">
         <v>846</v>
       </c>
-      <c r="C63" s="432"/>
-      <c r="D63" s="433"/>
+      <c r="C63" s="455"/>
+      <c r="D63" s="456"/>
     </row>
     <row r="64" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B64" s="223" t="s">
         <v>847</v>
       </c>
-      <c r="C64" s="432"/>
-      <c r="D64" s="433"/>
+      <c r="C64" s="455"/>
+      <c r="D64" s="456"/>
     </row>
     <row r="65" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B65" s="223" t="s">
         <v>848</v>
       </c>
-      <c r="C65" s="432"/>
-      <c r="D65" s="433"/>
+      <c r="C65" s="455"/>
+      <c r="D65" s="456"/>
     </row>
     <row r="66" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B66" s="223" t="s">
         <v>849</v>
       </c>
-      <c r="C66" s="432"/>
-      <c r="D66" s="433"/>
+      <c r="C66" s="455"/>
+      <c r="D66" s="456"/>
     </row>
     <row r="67" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B67" s="223" t="s">
         <v>850</v>
       </c>
-      <c r="C67" s="432"/>
-      <c r="D67" s="433"/>
+      <c r="C67" s="455"/>
+      <c r="D67" s="456"/>
     </row>
     <row r="68" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B68" s="223" t="s">
         <v>851</v>
       </c>
-      <c r="C68" s="432"/>
-      <c r="D68" s="433"/>
+      <c r="C68" s="455"/>
+      <c r="D68" s="456"/>
     </row>
     <row r="69" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B69" s="223" t="s">
         <v>852</v>
       </c>
-      <c r="C69" s="432"/>
-      <c r="D69" s="433"/>
+      <c r="C69" s="455"/>
+      <c r="D69" s="456"/>
     </row>
     <row r="70" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B70" s="223" t="s">
         <v>853</v>
       </c>
-      <c r="C70" s="432"/>
-      <c r="D70" s="433"/>
+      <c r="C70" s="455"/>
+      <c r="D70" s="456"/>
     </row>
     <row r="71" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B71" s="223" t="s">
         <v>854</v>
       </c>
-      <c r="C71" s="432"/>
-      <c r="D71" s="433"/>
+      <c r="C71" s="455"/>
+      <c r="D71" s="456"/>
     </row>
     <row r="72" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B72" s="223" t="s">
         <v>855</v>
       </c>
-      <c r="C72" s="432"/>
-      <c r="D72" s="433"/>
+      <c r="C72" s="455"/>
+      <c r="D72" s="456"/>
     </row>
     <row r="73" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B73" s="223" t="s">
         <v>856</v>
       </c>
-      <c r="C73" s="432"/>
-      <c r="D73" s="433"/>
+      <c r="C73" s="455"/>
+      <c r="D73" s="456"/>
     </row>
     <row r="74" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B74" s="223" t="s">
         <v>857</v>
       </c>
-      <c r="C74" s="432"/>
-      <c r="D74" s="433"/>
+      <c r="C74" s="455"/>
+      <c r="D74" s="456"/>
     </row>
     <row r="75" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B75" s="223" t="s">
         <v>858</v>
       </c>
-      <c r="C75" s="432"/>
-      <c r="D75" s="433"/>
+      <c r="C75" s="455"/>
+      <c r="D75" s="456"/>
     </row>
     <row r="76" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B76" s="223" t="s">
         <v>859</v>
       </c>
-      <c r="C76" s="432"/>
-      <c r="D76" s="433"/>
+      <c r="C76" s="455"/>
+      <c r="D76" s="456"/>
     </row>
     <row r="77" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B77" s="223" t="s">
         <v>860</v>
       </c>
-      <c r="C77" s="432"/>
-      <c r="D77" s="433"/>
+      <c r="C77" s="455"/>
+      <c r="D77" s="456"/>
     </row>
     <row r="78" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B78" s="223" t="s">
         <v>861</v>
       </c>
-      <c r="C78" s="432"/>
-      <c r="D78" s="433"/>
+      <c r="C78" s="455"/>
+      <c r="D78" s="456"/>
     </row>
     <row r="79" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B79" s="223" t="s">
         <v>862</v>
       </c>
-      <c r="C79" s="432"/>
-      <c r="D79" s="433"/>
+      <c r="C79" s="455"/>
+      <c r="D79" s="456"/>
     </row>
     <row r="80" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B80" s="223" t="s">
         <v>863</v>
       </c>
-      <c r="C80" s="432"/>
-      <c r="D80" s="433"/>
+      <c r="C80" s="455"/>
+      <c r="D80" s="456"/>
     </row>
     <row r="81" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B81" s="223" t="s">
         <v>864</v>
       </c>
-      <c r="C81" s="432"/>
-      <c r="D81" s="433"/>
+      <c r="C81" s="455"/>
+      <c r="D81" s="456"/>
     </row>
     <row r="82" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B82" s="223" t="s">
         <v>865</v>
       </c>
-      <c r="C82" s="432"/>
-      <c r="D82" s="433"/>
+      <c r="C82" s="455"/>
+      <c r="D82" s="456"/>
     </row>
     <row r="83" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B83" s="223" t="s">
         <v>866</v>
       </c>
-      <c r="C83" s="432"/>
-      <c r="D83" s="433"/>
+      <c r="C83" s="455"/>
+      <c r="D83" s="456"/>
     </row>
     <row r="84" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B84" s="223" t="s">
         <v>867</v>
       </c>
-      <c r="C84" s="432"/>
-      <c r="D84" s="433"/>
+      <c r="C84" s="455"/>
+      <c r="D84" s="456"/>
     </row>
     <row r="85" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B85" s="223" t="s">
         <v>868</v>
       </c>
-      <c r="C85" s="432"/>
-      <c r="D85" s="433"/>
+      <c r="C85" s="455"/>
+      <c r="D85" s="456"/>
     </row>
     <row r="86" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B86" s="223" t="s">
         <v>869</v>
       </c>
-      <c r="C86" s="432"/>
-      <c r="D86" s="433"/>
+      <c r="C86" s="455"/>
+      <c r="D86" s="456"/>
     </row>
     <row r="87" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B87" s="223" t="s">
         <v>870</v>
       </c>
-      <c r="C87" s="432"/>
-      <c r="D87" s="433"/>
+      <c r="C87" s="455"/>
+      <c r="D87" s="456"/>
     </row>
     <row r="88" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B88" s="223" t="s">
         <v>871</v>
       </c>
-      <c r="C88" s="432"/>
-      <c r="D88" s="433"/>
+      <c r="C88" s="455"/>
+      <c r="D88" s="456"/>
     </row>
     <row r="89" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B89" s="223" t="s">
         <v>872</v>
       </c>
-      <c r="C89" s="432"/>
-      <c r="D89" s="433"/>
+      <c r="C89" s="455"/>
+      <c r="D89" s="456"/>
     </row>
     <row r="90" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B90" s="223" t="s">
         <v>873</v>
       </c>
-      <c r="C90" s="432"/>
-      <c r="D90" s="433"/>
+      <c r="C90" s="455"/>
+      <c r="D90" s="456"/>
     </row>
     <row r="91" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B91" s="223" t="s">
         <v>874</v>
       </c>
-      <c r="C91" s="432"/>
-      <c r="D91" s="433"/>
+      <c r="C91" s="455"/>
+      <c r="D91" s="456"/>
     </row>
     <row r="92" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B92" s="223" t="s">
         <v>875</v>
       </c>
-      <c r="C92" s="432"/>
-      <c r="D92" s="433"/>
+      <c r="C92" s="455"/>
+      <c r="D92" s="456"/>
     </row>
     <row r="93" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B93" s="223" t="s">
         <v>876</v>
       </c>
-      <c r="C93" s="432"/>
-      <c r="D93" s="433"/>
+      <c r="C93" s="455"/>
+      <c r="D93" s="456"/>
     </row>
     <row r="94" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B94" s="223" t="s">
         <v>877</v>
       </c>
-      <c r="C94" s="432"/>
-      <c r="D94" s="433"/>
+      <c r="C94" s="455"/>
+      <c r="D94" s="456"/>
     </row>
     <row r="95" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B95" s="223" t="s">
         <v>878</v>
       </c>
-      <c r="C95" s="432"/>
-      <c r="D95" s="433"/>
+      <c r="C95" s="455"/>
+      <c r="D95" s="456"/>
     </row>
     <row r="96" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B96" s="223" t="s">
         <v>879</v>
       </c>
-      <c r="C96" s="432"/>
-      <c r="D96" s="433"/>
+      <c r="C96" s="455"/>
+      <c r="D96" s="456"/>
     </row>
     <row r="97" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B97" s="223" t="s">
         <v>880</v>
       </c>
-      <c r="C97" s="432"/>
-      <c r="D97" s="433"/>
+      <c r="C97" s="455"/>
+      <c r="D97" s="456"/>
     </row>
     <row r="98" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B98" s="223" t="s">
         <v>881</v>
       </c>
-      <c r="C98" s="432"/>
-      <c r="D98" s="433"/>
+      <c r="C98" s="455"/>
+      <c r="D98" s="456"/>
     </row>
     <row r="99" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B99" s="225" t="s">
         <v>882</v>
       </c>
-      <c r="C99" s="434"/>
-      <c r="D99" s="435"/>
+      <c r="C99" s="457"/>
+      <c r="D99" s="458"/>
     </row>
     <row r="100" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="101" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -23292,38 +23905,38 @@
       <c r="B102" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C102" s="436" t="s">
+      <c r="C102" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D102" s="437"/>
+      <c r="D102" s="444"/>
     </row>
     <row r="103" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B103" s="304" t="s">
         <v>883</v>
       </c>
-      <c r="C103" s="438"/>
-      <c r="D103" s="439"/>
+      <c r="C103" s="445"/>
+      <c r="D103" s="446"/>
     </row>
     <row r="104" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B104" s="223" t="s">
         <v>884</v>
       </c>
-      <c r="C104" s="440"/>
-      <c r="D104" s="441"/>
+      <c r="C104" s="447"/>
+      <c r="D104" s="448"/>
     </row>
     <row r="105" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B105" s="223" t="s">
         <v>885</v>
       </c>
-      <c r="C105" s="440"/>
-      <c r="D105" s="441"/>
+      <c r="C105" s="447"/>
+      <c r="D105" s="448"/>
     </row>
     <row r="106" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B106" s="225" t="s">
         <v>886</v>
       </c>
-      <c r="C106" s="442"/>
-      <c r="D106" s="443"/>
+      <c r="C106" s="449"/>
+      <c r="D106" s="450"/>
     </row>
     <row r="107" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="2:4" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -23341,19 +23954,19 @@
       <c r="B109" s="312" t="s">
         <v>751</v>
       </c>
-      <c r="C109" s="436" t="s">
+      <c r="C109" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D109" s="437"/>
+      <c r="D109" s="444"/>
     </row>
     <row r="110" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B110" s="304" t="s">
         <v>805</v>
       </c>
-      <c r="C110" s="444" t="s">
+      <c r="C110" s="459" t="s">
         <v>684</v>
       </c>
-      <c r="D110" s="450" t="s">
+      <c r="D110" s="465" t="s">
         <v>819</v>
       </c>
     </row>
@@ -23361,94 +23974,94 @@
       <c r="B111" s="223" t="s">
         <v>806</v>
       </c>
-      <c r="C111" s="445"/>
-      <c r="D111" s="448"/>
+      <c r="C111" s="460"/>
+      <c r="D111" s="463"/>
     </row>
     <row r="112" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B112" s="223" t="s">
         <v>807</v>
       </c>
-      <c r="C112" s="445"/>
-      <c r="D112" s="448"/>
+      <c r="C112" s="460"/>
+      <c r="D112" s="463"/>
     </row>
     <row r="113" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B113" s="223" t="s">
         <v>808</v>
       </c>
-      <c r="C113" s="445"/>
-      <c r="D113" s="448"/>
+      <c r="C113" s="460"/>
+      <c r="D113" s="463"/>
     </row>
     <row r="114" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B114" s="223" t="s">
         <v>809</v>
       </c>
-      <c r="C114" s="445"/>
-      <c r="D114" s="448"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="463"/>
     </row>
     <row r="115" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B115" s="223" t="s">
         <v>810</v>
       </c>
-      <c r="C115" s="445"/>
-      <c r="D115" s="448"/>
+      <c r="C115" s="460"/>
+      <c r="D115" s="463"/>
     </row>
     <row r="116" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B116" s="223" t="s">
         <v>811</v>
       </c>
-      <c r="C116" s="445"/>
-      <c r="D116" s="448"/>
+      <c r="C116" s="460"/>
+      <c r="D116" s="463"/>
     </row>
     <row r="117" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B117" s="223" t="s">
         <v>812</v>
       </c>
-      <c r="C117" s="445"/>
-      <c r="D117" s="448"/>
+      <c r="C117" s="460"/>
+      <c r="D117" s="463"/>
     </row>
     <row r="118" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B118" s="223" t="s">
         <v>813</v>
       </c>
-      <c r="C118" s="445"/>
-      <c r="D118" s="448"/>
+      <c r="C118" s="460"/>
+      <c r="D118" s="463"/>
     </row>
     <row r="119" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B119" s="223" t="s">
         <v>814</v>
       </c>
-      <c r="C119" s="445"/>
-      <c r="D119" s="448"/>
+      <c r="C119" s="460"/>
+      <c r="D119" s="463"/>
     </row>
     <row r="120" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B120" s="223" t="s">
         <v>815</v>
       </c>
-      <c r="C120" s="446"/>
-      <c r="D120" s="448"/>
+      <c r="C120" s="461"/>
+      <c r="D120" s="463"/>
     </row>
     <row r="121" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B121" s="223" t="s">
         <v>816</v>
       </c>
-      <c r="C121" s="447" t="s">
+      <c r="C121" s="462" t="s">
         <v>685</v>
       </c>
-      <c r="D121" s="448"/>
+      <c r="D121" s="463"/>
     </row>
     <row r="122" spans="2:4" s="36" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B122" s="223" t="s">
         <v>817</v>
       </c>
-      <c r="C122" s="448"/>
-      <c r="D122" s="448"/>
+      <c r="C122" s="463"/>
+      <c r="D122" s="463"/>
     </row>
     <row r="123" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B123" s="225" t="s">
         <v>818</v>
       </c>
-      <c r="C123" s="449"/>
-      <c r="D123" s="449"/>
+      <c r="C123" s="464"/>
+      <c r="D123" s="464"/>
     </row>
     <row r="124" spans="2:4" s="36" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="240"/>
@@ -23470,22 +24083,36 @@
       <c r="B126" s="312" t="s">
         <v>821</v>
       </c>
-      <c r="C126" s="436" t="s">
+      <c r="C126" s="443" t="s">
         <v>670</v>
       </c>
-      <c r="D126" s="437"/>
+      <c r="D126" s="444"/>
     </row>
     <row r="127" spans="2:4" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B127" s="330" t="s">
         <v>820</v>
       </c>
-      <c r="C127" s="428" t="s">
+      <c r="C127" s="451" t="s">
         <v>822</v>
       </c>
-      <c r="D127" s="429"/>
+      <c r="D127" s="452"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="C127:D127"/>
+    <mergeCell ref="C60:D99"/>
+    <mergeCell ref="C102:D102"/>
+    <mergeCell ref="C103:D106"/>
+    <mergeCell ref="C109:D109"/>
+    <mergeCell ref="C126:D126"/>
+    <mergeCell ref="C110:C120"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="D110:D123"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="C59:D59"/>
     <mergeCell ref="D40:D43"/>
     <mergeCell ref="D6:D10"/>
     <mergeCell ref="C5:D5"/>
@@ -23496,26 +24123,12 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="C28:D36"/>
     <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C127:D127"/>
-    <mergeCell ref="C60:D99"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="C103:D106"/>
-    <mergeCell ref="C109:D109"/>
-    <mergeCell ref="C126:D126"/>
-    <mergeCell ref="C110:C120"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="D110:D123"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B8:L19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23731,7 +24344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:D23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -23894,7 +24507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Tabelle5"/>
   <dimension ref="B1:F7"/>
@@ -24002,7 +24615,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:D16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -24064,22 +24677,22 @@
       <c r="B12" s="400" t="s">
         <v>336</v>
       </c>
-      <c r="C12" s="458" t="s">
+      <c r="C12" s="470" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="459"/>
+      <c r="D12" s="471"/>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="456" t="s">
+      <c r="B13" s="468" t="s">
         <v>920</v>
       </c>
-      <c r="C13" s="454" t="s">
+      <c r="C13" s="466" t="s">
         <v>919</v>
       </c>
-      <c r="D13" s="455"/>
+      <c r="D13" s="467"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="457"/>
+      <c r="B14" s="469"/>
       <c r="C14" s="383" t="s">
         <v>637</v>
       </c>
@@ -24122,154 +24735,4 @@
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Tabelle4"/>
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="2.5703125" style="36" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" style="15" customWidth="1"/>
-    <col min="3" max="3" width="22.42578125" style="15" customWidth="1"/>
-    <col min="4" max="4" width="22" style="15" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" style="15" customWidth="1"/>
-    <col min="6" max="7" width="22" style="15" customWidth="1"/>
-    <col min="8" max="16384" width="11.42578125" style="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:12" s="36" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D2" s="328" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="3:12" s="36" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="39" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="4" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="7" t="s">
-        <v>680</v>
-      </c>
-      <c r="D4" s="87" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="5" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C5" s="59">
-        <v>400</v>
-      </c>
-      <c r="D5" s="24">
-        <v>0</v>
-      </c>
-      <c r="E5" s="36"/>
-      <c r="F5" s="36"/>
-    </row>
-    <row r="6" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C6" s="10">
-        <v>800</v>
-      </c>
-      <c r="D6" s="11">
-        <v>0.47</v>
-      </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-    </row>
-    <row r="7" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C7" s="10">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="11">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="E7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-    </row>
-    <row r="8" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C8" s="10">
-        <v>1200</v>
-      </c>
-      <c r="D8" s="11">
-        <v>0.53</v>
-      </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="36"/>
-    </row>
-    <row r="9" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C9" s="10">
-        <v>1400</v>
-      </c>
-      <c r="D9" s="11">
-        <v>0.46</v>
-      </c>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-    </row>
-    <row r="10" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C10" s="10">
-        <v>1500</v>
-      </c>
-      <c r="D10" s="11">
-        <v>0.43</v>
-      </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="J10" s="36"/>
-    </row>
-    <row r="11" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C11" s="10">
-        <v>1750</v>
-      </c>
-      <c r="D11" s="11">
-        <v>0.22</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-    </row>
-    <row r="12" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C12" s="10">
-        <v>1800</v>
-      </c>
-      <c r="D12" s="11">
-        <v>0.2</v>
-      </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-    </row>
-    <row r="13" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C13" s="10">
-        <v>2000</v>
-      </c>
-      <c r="D13" s="11">
-        <v>0.11</v>
-      </c>
-      <c r="E13" s="36"/>
-      <c r="F13" s="36"/>
-    </row>
-    <row r="14" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="60">
-        <v>2500</v>
-      </c>
-      <c r="D14" s="61">
-        <v>0.11</v>
-      </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>